--- a/docs/templates/名单导入模板.xlsx
+++ b/docs/templates/名单导入模板.xlsx
@@ -11,15 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>姓名</t>
   </si>
   <si>
+    <t>单位</t>
+  </si>
+  <si>
     <t>身份证号</t>
   </si>
   <si>
     <t>【示例】请删除本行后填写真实考生信息；姓名与身份证号须与证件一致（除首尾空格外须完全一致）</t>
+  </si>
+  <si>
+    <t>示例单位</t>
   </si>
   <si>
     <t>11010519491231002X</t>
@@ -404,27 +410,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
